--- a/artfynd/A 21329-2026 artfynd.xlsx
+++ b/artfynd/A 21329-2026 artfynd.xlsx
@@ -675,32 +675,32 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>134192723</v>
+        <v>134192744</v>
       </c>
       <c r="B2" t="n">
-        <v>58136</v>
+        <v>57972</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>103021</v>
+        <v>100049</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
@@ -710,12 +710,12 @@
       </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t>upprörd, varnande</t>
+          <t>lockläte, övriga läten</t>
         </is>
       </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>A 21329-2026, Sm</t>
+          <t>A 21329-2026, A 21329-2026, Sm</t>
         </is>
       </c>
       <c r="Q2" t="n">
@@ -754,7 +754,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>10:17</t>
+          <t>10:18</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -764,7 +764,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>10:17</t>
+          <t>10:18</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -791,14 +791,14 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>134192744</v>
+        <v>134322255</v>
       </c>
       <c r="B3" t="n">
         <v>57972</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
@@ -824,24 +824,27 @@
           <t>1</t>
         </is>
       </c>
+      <c r="K3" t="inlineStr"/>
+      <c r="L3" t="inlineStr"/>
       <c r="M3" t="inlineStr">
         <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>A 21329-2026, A 21329-2026, Sm</t>
+          <t>A 21329-2026, Sm</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>565233</v>
+        <v>565176</v>
       </c>
       <c r="R3" t="n">
-        <v>6436316</v>
+        <v>6436269</v>
       </c>
       <c r="S3" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -868,19 +871,9 @@
           <t>2026-06-07</t>
         </is>
       </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>10:18</t>
-        </is>
-      </c>
       <c r="AA3" t="inlineStr">
         <is>
           <t>2026-06-07</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>10:18</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -907,10 +900,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>134322255</v>
+        <v>134192723</v>
       </c>
       <c r="B4" t="n">
-        <v>57972</v>
+        <v>58136</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -918,21 +911,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>100049</v>
+        <v>103021</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
@@ -940,27 +933,24 @@
           <t>1</t>
         </is>
       </c>
-      <c r="K4" t="inlineStr"/>
-      <c r="L4" t="inlineStr"/>
       <c r="M4" t="inlineStr">
         <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N4" t="inlineStr"/>
+          <t>upprörd, varnande</t>
+        </is>
+      </c>
       <c r="P4" t="inlineStr">
         <is>
           <t>A 21329-2026, Sm</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>565176</v>
+        <v>565233</v>
       </c>
       <c r="R4" t="n">
-        <v>6436269</v>
+        <v>6436316</v>
       </c>
       <c r="S4" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -987,9 +977,19 @@
           <t>2026-06-07</t>
         </is>
       </c>
+      <c r="Z4" t="inlineStr">
+        <is>
+          <t>10:17</t>
+        </is>
+      </c>
       <c r="AA4" t="inlineStr">
         <is>
           <t>2026-06-07</t>
+        </is>
+      </c>
+      <c r="AB4" t="inlineStr">
+        <is>
+          <t>10:17</t>
         </is>
       </c>
       <c r="AD4" t="b">
